--- a/output/data_quality_scorecard.xlsx
+++ b/output/data_quality_scorecard.xlsx
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61741</v>
+        <v>80976</v>
       </c>
     </row>
     <row r="10">
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44.83</v>
+        <v>37.93</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Data is clean for this dimension. Rule passed. Preventive control is documented to maintain data quality.</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>Collect email through next customer interaction or digital prompt</t>
@@ -2114,7 +2118,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2163,7 +2166,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Data is clean for this dimension. Rule passed. Preventive control is documented to maintain data quality.</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>Update phone during next branch visit or call</t>
@@ -2194,7 +2201,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2331,7 +2337,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Data is clean for this dimension. Rule passed. Preventive control is documented to maintain data quality.</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>Investigate telemetry pipeline for logging gaps</t>
@@ -2362,7 +2372,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2411,7 +2420,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Data is clean for this dimension. Rule passed. Preventive control is documented to maintain data quality.</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>Entity resolution: review and merge confirmed duplicates with audit trail</t>
@@ -2442,7 +2455,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2819,7 +2831,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Invalid Indian phone number format</t>
+          <t>Phone stored with 91 country-code prefix (12 digits) instead of 10-digit Indian mobile number</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2833,20 +2845,24 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>10,200 (100.0%) customer phone records include the 91 country code prefix. Systems expecting 10-digit format will fail SMS delivery, OTP and contact centre matching.</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Validate and correct phone during next interaction</t>
+          <t>Strip leading 91 prefix; enforce 10-digit ^[6-9]\d{9}$ regex at ingestion gateway</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2874,7 +2890,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2899,7 +2914,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Invalid KYC_Status values (expected: Verified, Pending, Failed)</t>
+          <t>KYC_Status uses non-standard value "Completed" instead of approved value "Verified"</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2913,20 +2928,24 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>9035</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>88.58</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>9,035 (88.58%) customer records have KYC_Status="Completed" which is not the approved regulatory vocabulary. Regulatory reports filtering on "Verified" will undercount compliant customers.</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Map non-standard values to canonical KYC statuses</t>
+          <t>Remap Completed → Verified; enforce enum {Verified, Pending, Failed} in source system</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2954,7 +2973,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3003,7 +3021,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Data is clean for this dimension. Rule passed. Preventive control is documented to maintain data quality.</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>Map non-standard values to canonical segments</t>
@@ -3034,7 +3056,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3083,7 +3104,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Data is clean for this dimension. Rule passed. Preventive control is documented to maintain data quality.</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>Correct NPA flags based on DPD rules</t>
@@ -3114,7 +3139,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3163,7 +3187,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Data is clean for this dimension. Rule passed. Preventive control is documented to maintain data quality.</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>Cap to valid range or investigate survey system</t>
@@ -3194,7 +3222,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3243,7 +3270,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Data is clean for this dimension. Rule passed. Preventive control is documented to maintain data quality.</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>Investigate source system DPD calculation logic</t>
@@ -3274,7 +3305,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3323,7 +3353,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Data is clean for this dimension. Rule passed. Preventive control is documented to maintain data quality.</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>Review against product-level rate schedules</t>
@@ -3354,7 +3388,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3403,7 +3436,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Data is clean for this dimension. Rule passed. Preventive control is documented to maintain data quality.</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>Align NPA_Flag with DPD-based classification rules</t>
@@ -3434,7 +3471,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4099,7 +4135,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Data is clean for this dimension. Rule passed. Preventive control is documented to maintain data quality.</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>Escalate unresolved complaints; validate TAT calculation</t>
@@ -4130,7 +4170,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4637,7 +4676,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>Collect email through next customer interaction or digital prompt</t>
@@ -4668,7 +4706,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4717,7 +4754,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>Update phone during next branch visit or call</t>
@@ -4748,7 +4784,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4885,7 +4920,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>Investigate telemetry pipeline for logging gaps</t>
@@ -4916,7 +4950,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5071,7 +5104,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>Entity resolution: review and merge confirmed duplicates with audit trail</t>
@@ -5102,7 +5134,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5609,7 +5640,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>Validate and correct phone during next interaction</t>
@@ -5640,7 +5670,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5689,7 +5718,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>Map non-standard values to canonical KYC statuses</t>
@@ -5720,7 +5748,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5769,7 +5796,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>Map non-standard values to canonical segments</t>
@@ -5800,7 +5826,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5849,7 +5874,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>Correct NPA flags based on DPD rules</t>
@@ -5880,7 +5904,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5929,7 +5952,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>Cap to valid range or investigate survey system</t>
@@ -5960,7 +5982,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6009,7 +6030,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>Investigate source system DPD calculation logic</t>
@@ -6040,7 +6060,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6089,7 +6108,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>Review against product-level rate schedules</t>
@@ -6120,7 +6138,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6363,7 +6380,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>Align NPA_Flag with DPD-based classification rules</t>
@@ -6394,7 +6410,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7447,7 +7462,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>Escalate unresolved complaints; validate TAT calculation</t>
@@ -7478,7 +7492,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
